--- a/data/trans_orig/IP36_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP36_2023-Edad-trans_orig.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables originales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:W54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,12 +524,18 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos según su situación laboral actual en 2023 (Tasa respuesta: 100,0%)</t>
+          <t>Adultos según su situación laboral actual / solo 2023 en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -542,24 +548,30 @@
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
       <c r="K1" s="3" t="n"/>
       <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="M1" s="3" t="n"/>
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
+      <c r="U1" s="3" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,65 +588,95 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -658,6 +700,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -670,67 +718,109 @@
           <t>Otros</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>2114</v>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>860</v>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>2974</v>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2439</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -738,70 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Incapacidad/invalidez permanente</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>445</v>
+          <t>Voluntariado social</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1622</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>6382</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3094</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>445</v>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2482</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>7326</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -809,70 +941,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Estudiante</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0</v>
+          <t>Incapacidad/invalidez permanente</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2502</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>396</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>396</v>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>2381</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -880,70 +1054,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Sus labores/Ama de casa</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>7216</v>
+          <t>Estudiante</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>7150</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>396</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>14366</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2216</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2283</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -951,70 +1167,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Jubilado (trabajó anteriormente)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0</v>
+          <t>Sus labores/Ama de casa/Trabajo doméstico no remunerado</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7216</t>
+        </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>578</v>
+          <t>12,55%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>21,06%</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>578</v>
+          <t>4029</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>11661</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>11,64%</t>
+        </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>14366</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>9777</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>20233</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -1022,70 +1280,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Busca primer empleo</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>540</v>
+          <t>Jubilado/a (trabajó anteriormente)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3360</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>1038</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>1577</v>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1093,70 +1393,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Está en el paro y ha trabajado antes</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>7758</v>
+          <t>Busca primer empleo</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>8510</v>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>16269</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3459</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4228</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -1164,70 +1506,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Trabaja</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>39438</v>
+          <t>Está en el paro y ha trabajado antes</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7758</t>
+        </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>12014</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>42912</v>
+          <t>13,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20,89%</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>82351</v>
+          <t>4595</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>13987</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>13,85%</t>
+        </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>16269</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>10927</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>23609</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>13,68%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>9,19%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -1235,216 +1619,342 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>57511</v>
+          <t>Trabaja</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>33869</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>44900</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>116</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>61444</v>
+          <t>68,58%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>58,89%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>78,07%</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>42912</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>225</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>118955</v>
+          <t>36777</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>47971</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>69,84%</t>
+        </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>82351</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>74109</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>89853</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>69,23%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>62,3%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>75,54%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
+      <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>2404</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>57511</t>
+        </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>57511</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>57511</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>519</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>61444</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>2923</v>
+          <t>61444</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>61444</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>118955</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>118955</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>118955</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n"/>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Incapacidad/invalidez permanente</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>2693</v>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>4169</v>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>6862</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>2430</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -1452,70 +1962,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Estudiante</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>2729</v>
+          <t>Voluntariado social</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>552</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>2937</v>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>519</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>5666</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2610</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2431</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1523,70 +2075,112 @@
       <c r="A16" s="1" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Sus labores/Ama de casa</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>19676</v>
+          <t>Incapacidad/invalidez permanente</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2693</t>
+        </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>25967</v>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>45643</v>
+          <t>1657</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8623</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>6862</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>3608</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>12383</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -1594,70 +2188,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Jubilado (trabajó anteriormente)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>1450</v>
+          <t>Estudiante</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>3825</v>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>5275</v>
+          <t>1084</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>7251</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>5666</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>3011</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>10832</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1665,70 +2301,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Busca primer empleo</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>0</v>
+          <t>Sus labores/Ama de casa/Trabajo doméstico no remunerado</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19676</t>
+        </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27967</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+          <t>12,35%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>17,56%</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25967</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>0</v>
+          <t>18706</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>35130</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>14,22%</t>
+        </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>45643</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>35502</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>56117</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>13,35%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>10,39%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -1736,70 +2414,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Está en el paro y ha trabajado antes</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>21402</v>
+          <t>Jubilado/a (trabajó anteriormente)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>24720</v>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>46122</v>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8946</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>5275</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>10519</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -1807,70 +2527,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Trabaja</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>108945</v>
+          <t>Busca primer empleo</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>120417</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>360</v>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>229362</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1878,145 +2640,225 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>258</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>159299</v>
+          <t>Está en el paro y ha trabajado antes</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>21402</t>
+        </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>32550</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>276</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>182554</v>
+          <t>13,44%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>9,23%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>20,43%</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>534</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>341853</v>
+          <t>18125</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>33251</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>46122</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>35966</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>59125</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>13,49%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>10,52%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>0</v>
+          <t>Trabaja</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>108945</t>
+        </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>98470</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>118564</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>2799</v>
+          <t>68,39%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>61,81%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>74,43%</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>180</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>120417</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>2799</v>
+          <t>108650</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>131126</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>65,96%</t>
+        </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>229362</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>214589</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>244469</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>67,09%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>62,77%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>71,51%</t>
         </is>
       </c>
     </row>
@@ -2024,141 +2866,229 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Incapacidad/invalidez permanente</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>3439</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>159299</t>
+        </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>159299</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>159299</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>4088</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>276</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>182554</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>7527</v>
+          <t>182554</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>182554</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>341853</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>341853</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>341853</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n"/>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Estudiante</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>6423</v>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>7981</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>14404</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2166,70 +3096,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Sus labores/Ama de casa</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>29357</v>
+          <t>Voluntariado social</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>27853</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>57211</v>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>7357</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -2237,70 +3209,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Jubilado (trabajó anteriormente)</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>4470</v>
+          <t>Incapacidad/invalidez permanente</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3439</t>
+        </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>7936</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>2663</v>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N26" s="2" t="n">
-        <v>7133</v>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>10411</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>7527</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>3243</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>14219</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -2308,70 +3322,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Busca primer empleo</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>798</v>
+          <t>Estudiante</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>6423</t>
+        </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11958</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>427</v>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>6,88%</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>1225</v>
+          <t>3920</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>15223</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>14404</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>8667</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>22888</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -2379,70 +3435,112 @@
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Está en el paro y ha trabajado antes</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>22308</v>
+          <t>Sus labores/Ama de casa/Trabajo doméstico no remunerado</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>29357</t>
+        </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>20717</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>40810</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>18917</v>
+          <t>16,88%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>23,47%</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>27853</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="N28" s="2" t="n">
-        <v>41225</v>
+          <t>20384</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>38501</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>13,11%</t>
+        </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>57211</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>71916</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>14,81%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>11,87%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -2450,70 +3548,112 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Trabaja</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>107092</v>
+          <t>Jubilado/a (trabajó anteriormente)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>4470</t>
+        </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>166</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>147763</v>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>5,57%</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>316</v>
-      </c>
-      <c r="N29" s="2" t="n">
-        <v>254856</v>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>7006</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>7133</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>13410</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -2521,145 +3661,225 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>234</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>173888</v>
+          <t>Busca primer empleo</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>243</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>212490</v>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>427</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>477</v>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>386378</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2771</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>4480</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
+      <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>1358</v>
+          <t>Está en el paro y ha trabajado antes</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>22308</t>
+        </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>15221</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>32667</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>2412</v>
+          <t>12,83%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>18,79%</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>3771</v>
+          <t>12694</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>29018</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>8,9%</t>
+        </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>41225</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>29840</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>54713</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -2667,70 +3887,112 @@
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Incapacidad/invalidez permanente</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>4262</v>
+          <t>Trabaja</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>107092</t>
+        </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>94628</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>118631</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>6568</v>
+          <t>61,59%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>54,42%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>68,22%</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>166</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>147763</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="N32" s="2" t="n">
-        <v>10831</v>
+          <t>133810</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>159269</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>69,54%</t>
+        </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>254856</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>235785</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>271238</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>65,96%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>61,02%</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>70,2%</t>
         </is>
       </c>
     </row>
@@ -2738,141 +4000,229 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Estudiante</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>12322</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>173888</t>
+        </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>173888</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>173888</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>6292</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>243</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>212490</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="N33" s="2" t="n">
-        <v>18613</v>
+          <t>212490</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>212490</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>386378</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>386378</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>386378</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n"/>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Sus labores/Ama de casa</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>45324</v>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>44788</v>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="N34" s="2" t="n">
-        <v>90112</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2880,70 +4230,112 @@
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Jubilado (trabajó anteriormente)</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>5618</v>
+          <t>Voluntariado social</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>5536</v>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="N35" s="2" t="n">
-        <v>11153</v>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>7409</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>3771</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>8746</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -2951,70 +4343,112 @@
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Busca primer empleo</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>529</v>
+          <t>Incapacidad/invalidez permanente</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>4262</t>
+        </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9651</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>1236</v>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>1764</v>
+          <t>3056</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>12092</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>10831</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>5918</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>18533</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -3022,70 +4456,112 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Está en el paro y ha trabajado antes</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>55645</v>
+          <t>Estudiante</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>12322</t>
+        </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>19557</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>46896</v>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="N37" s="2" t="n">
-        <v>102540</v>
+          <t>2628</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>14235</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>18613</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>11967</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>28528</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -3093,70 +4569,112 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Trabaja</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>210</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>150401</v>
+          <t>Sus labores/Ama de casa/Trabajo doméstico no remunerado</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>45324</t>
+        </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>31337</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>59292</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>215</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>191755</v>
+          <t>16,45%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>11,38%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>21,52%</t>
+        </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>44788</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="n">
-        <v>425</v>
-      </c>
-      <c r="N38" s="2" t="n">
-        <v>342155</v>
+          <t>33132</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>59303</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>14,66%</t>
+        </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>90112</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>69686</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>108125</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>15,51%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>12,0%</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -3164,145 +4682,225 @@
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>342</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>275458</v>
+          <t>Jubilado/a (trabajó anteriormente)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>5618</t>
+        </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>10700</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>342</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>305483</v>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="n">
-        <v>684</v>
-      </c>
-      <c r="N39" s="2" t="n">
-        <v>580940</v>
+          <t>2402</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>10785</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>11153</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>6298</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>18082</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A40" s="1" t="n"/>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>5875</v>
+          <t>Busca primer empleo</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>6591</v>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="N40" s="2" t="n">
-        <v>12466</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>6732</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>1764</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>8494</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -3310,70 +4908,112 @@
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Incapacidad/invalidez permanente</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>10839</v>
+          <t>Está en el paro y ha trabajado antes</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>55645</t>
+        </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>27328</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>121004</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>14826</v>
+          <t>20,2%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>43,93%</t>
+        </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>46896</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="N41" s="2" t="n">
-        <v>25665</v>
+          <t>34954</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>67373</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>15,35%</t>
+        </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>102540</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>71501</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>177688</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>17,65%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -3381,70 +5021,112 @@
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Estudiante</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>21474</v>
+          <t>Trabaja</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>150401</t>
+        </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>104637</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>172599</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>17605</v>
+          <t>54,6%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>37,99%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>62,66%</t>
+        </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>215</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>191755</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="N42" s="2" t="n">
-        <v>39079</v>
+          <t>171779</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>211917</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>62,77%</t>
+        </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>342155</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>293730</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>371745</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>58,9%</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>50,56%</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>63,99%</t>
         </is>
       </c>
     </row>
@@ -3452,141 +5134,229 @@
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Sus labores/Ama de casa</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>101573</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>275458</t>
+        </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>105758</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>342</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>305483</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="n">
-        <v>273</v>
-      </c>
-      <c r="N43" s="2" t="n">
-        <v>207331</v>
+          <t>305483</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>305483</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>580940</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>580940</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>580940</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n"/>
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Jubilado (trabajó anteriormente)</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>11538</v>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>12601</v>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="N44" s="2" t="n">
-        <v>24139</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -3594,70 +5364,112 @@
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Busca primer empleo</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>1866</v>
+          <t>Voluntariado social</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>4892</t>
+        </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>2700</v>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="N45" s="2" t="n">
-        <v>4566</v>
+          <t>3073</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>12382</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>11483</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>6902</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>18379</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -3665,70 +5477,112 @@
       <c r="A46" s="1" t="n"/>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Está en el paro y ha trabajado antes</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>107113</v>
+          <t>Incapacidad/invalidez permanente</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10839</t>
+        </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>99043</v>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>14826</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>238</v>
-      </c>
-      <c r="N46" s="2" t="n">
-        <v>206155</v>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>23687</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>25665</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>18583</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>35762</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -3736,70 +5590,112 @@
       <c r="A47" s="1" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Trabaja</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>615</v>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>405877</v>
+          <t>Estudiante</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>21474</t>
+        </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>14146</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>29512</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>643</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>502848</v>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>17605</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>1258</v>
-      </c>
-      <c r="N47" s="2" t="n">
-        <v>908725</v>
+          <t>10526</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>26271</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>39079</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>29699</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>51721</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -3807,75 +5703,682 @@
       <c r="A48" s="1" t="n"/>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>943</v>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>666155</v>
+          <t>Sus labores/Ama de casa/Trabajo doméstico no remunerado</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>101573</t>
+        </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>83262</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>118326</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>977</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>761972</v>
+          <t>15,25%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>17,76%</t>
+        </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>134</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>105758</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>1920</v>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>1428127</v>
+          <t>89898</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>126105</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>13,88%</t>
+        </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>207331</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>182861</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>234940</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>14,52%</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="1" t="n"/>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Jubilado/a (trabajó anteriormente)</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11538</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>6732</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>18771</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>12601</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>7279</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>20055</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>24139</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>16336</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>32794</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n"/>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Busca primer empleo</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>1866</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>7805</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>4566</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>1727</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>9164</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n"/>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Está en el paro y ha trabajado antes</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>107113</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>77718</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>181520</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>16,08%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>27,25%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>99043</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>82035</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>120769</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>15,85%</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>206155</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>168947</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>286726</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14,44%</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>11,83%</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>20,08%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n"/>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Trabaja</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>405877</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>353793</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>433853</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>60,93%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>53,11%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>65,13%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>502848</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>475308</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>529194</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>65,99%</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>62,38%</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>69,45%</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>908725</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>846932</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>949756</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>63,63%</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>59,3%</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>66,5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n"/>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>666155</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>666155</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>666155</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>1428127</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>1428127</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>1428127</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -3883,15 +6386,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A13:A21"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A4:A12"/>
-    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A44:A53"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A34:A43"/>
+    <mergeCell ref="A4:A13"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A31:A39"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="A40:A48"/>
+    <mergeCell ref="A14:A23"/>
+    <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="C1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
